--- a/data/trans_orig/IP2904-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP2904-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39681</t>
+          <t>39490</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55567</t>
+          <t>55500</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28324</t>
+          <t>28421</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43030</t>
+          <t>43640</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73224</t>
+          <t>72925</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95477</t>
+          <t>93696</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>48,37%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19868</t>
+          <t>17909</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32766</t>
+          <t>32538</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23884</t>
+          <t>24267</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37949</t>
+          <t>38865</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47410</t>
+          <t>47379</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67758</t>
+          <t>66628</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,4%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18879</t>
+          <t>19083</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33323</t>
+          <t>33372</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20969</t>
+          <t>20730</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35811</t>
+          <t>35149</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44423</t>
+          <t>44329</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63443</t>
+          <t>63524</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28273</t>
+          <t>28476</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42419</t>
+          <t>41964</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29083</t>
+          <t>29476</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43764</t>
+          <t>42896</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62721</t>
+          <t>61201</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>82041</t>
+          <t>82731</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,57%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15724</t>
+          <t>15618</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28601</t>
+          <t>28598</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17885</t>
+          <t>17918</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31257</t>
+          <t>30790</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36700</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>54743</t>
+          <t>54779</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,82%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19310</t>
+          <t>19673</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32772</t>
+          <t>33281</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18041</t>
+          <t>18439</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31439</t>
+          <t>31093</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40453</t>
+          <t>40691</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59199</t>
+          <t>60364</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>36,17%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25064</t>
+          <t>25521</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38081</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28182</t>
+          <t>27819</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>43314</t>
+          <t>43122</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>56876</t>
+          <t>56755</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>77536</t>
+          <t>76828</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>47,89%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10006</t>
+          <t>10342</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20772</t>
+          <t>20952</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25391</t>
+          <t>25677</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40445</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38663</t>
+          <t>39217</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>57705</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,97%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13529</t>
+          <t>13486</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24863</t>
+          <t>24655</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,47 +1885,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>20,63%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>37,71%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>26683</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>19661</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>33666</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>28,08%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>20,69%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>38,03%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>26683</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>20242</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>33881</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>28,08%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>21,3%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35881</t>
+          <t>36453</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55216</t>
+          <t>55058</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77826</t>
+          <t>78999</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>100398</t>
+          <t>100014</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70788</t>
+          <t>70226</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92526</t>
+          <t>91981</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>152596</t>
+          <t>154735</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>184523</t>
+          <t>186070</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>48,41%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38986</t>
+          <t>38670</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57540</t>
+          <t>56464</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44913</t>
+          <t>46166</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66865</t>
+          <t>66338</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>90469</t>
+          <t>88314</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>117837</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,4%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45639</t>
+          <t>45900</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>65913</t>
+          <t>64964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>46406</t>
+          <t>46735</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66310</t>
+          <t>66588</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>98196</t>
+          <t>97932</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>126750</t>
+          <t>125335</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,61%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38093</t>
+          <t>38388</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>54913</t>
+          <t>54160</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>58904</t>
+          <t>58028</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>76332</t>
+          <t>75776</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>102322</t>
+          <t>100223</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>124512</t>
+          <t>125552</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>56,46%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11179</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23678</t>
+          <t>23130</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15431</t>
+          <t>15337</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28391</t>
+          <t>28434</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>30298</t>
+          <t>29745</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>48272</t>
+          <t>47795</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27558</t>
+          <t>28575</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43646</t>
+          <t>43779</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27220</t>
+          <t>27809</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42872</t>
+          <t>43424</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59956</t>
+          <t>59158</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>81756</t>
+          <t>81501</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,65%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18690</t>
+          <t>18785</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32011</t>
+          <t>32159</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25939</t>
+          <t>24844</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>39202</t>
+          <t>38509</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>48219</t>
+          <t>48425</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>66986</t>
+          <t>67138</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,9%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11030</t>
+          <t>11634</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23073</t>
+          <t>23845</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>7088</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16856</t>
+          <t>17578</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21295</t>
+          <t>21477</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36403</t>
+          <t>37074</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,45%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>24938</t>
+          <t>24779</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>38405</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17114</t>
+          <t>17178</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29808</t>
+          <t>30106</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>44593</t>
+          <t>44922</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>63668</t>
+          <t>63800</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,52%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>255644</t>
+          <t>254415</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>294736</t>
+          <t>294457</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>267782</t>
+          <t>267702</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>309056</t>
+          <t>308150</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>533894</t>
+          <t>536002</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>590188</t>
+          <t>596360</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>47,04%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>125349</t>
+          <t>125444</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>159042</t>
+          <t>159392</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>159821</t>
+          <t>159330</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>196749</t>
+          <t>195592</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>294935</t>
+          <t>292108</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>345704</t>
+          <t>344460</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,17%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>175542</t>
+          <t>175135</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>212007</t>
+          <t>212539</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>172233</t>
+          <t>174238</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>211442</t>
+          <t>211026</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>362992</t>
+          <t>358498</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>413976</t>
+          <t>411194</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,43%</t>
         </is>
       </c>
     </row>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28118</t>
+          <t>29140</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43569</t>
+          <t>44314</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32442</t>
+          <t>32146</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46656</t>
+          <t>47687</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65161</t>
+          <t>65561</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>86104</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,71%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14024</t>
+          <t>13768</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26792</t>
+          <t>27183</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23402</t>
+          <t>22959</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37564</t>
+          <t>37534</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40414</t>
+          <t>41301</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59335</t>
+          <t>60031</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,66%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25491</t>
+          <t>24700</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40186</t>
+          <t>39626</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10127</t>
+          <t>10006</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21281</t>
+          <t>21798</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38744</t>
+          <t>37694</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>57762</t>
+          <t>57082</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,96%</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32883</t>
+          <t>32274</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47405</t>
+          <t>47340</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45339</t>
+          <t>45606</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61074</t>
+          <t>61034</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>81761</t>
+          <t>82901</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>104374</t>
+          <t>104330</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,81%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16851</t>
+          <t>17636</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30950</t>
+          <t>31196</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17767</t>
+          <t>17243</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31797</t>
+          <t>31059</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>39820</t>
+          <t>38741</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>59375</t>
+          <t>57508</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17660</t>
+          <t>17935</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31679</t>
+          <t>31556</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9435</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20903</t>
+          <t>21052</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30216</t>
+          <t>31006</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48488</t>
+          <t>48557</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,9%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38962</t>
+          <t>37256</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53193</t>
+          <t>52697</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29461</t>
+          <t>30117</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44489</t>
+          <t>45141</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>71410</t>
+          <t>72423</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>92900</t>
+          <t>93404</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>56,19%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15622</t>
+          <t>16095</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28624</t>
+          <t>29448</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25826</t>
+          <t>25309</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40605</t>
+          <t>39824</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44114</t>
+          <t>44651</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63248</t>
+          <t>63608</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,27%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10470</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21944</t>
+          <t>22093</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>8850</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20092</t>
+          <t>20530</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21945</t>
+          <t>22410</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37653</t>
+          <t>38949</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83424</t>
+          <t>83378</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>105315</t>
+          <t>105586</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92808</t>
+          <t>91677</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>116252</t>
+          <t>115876</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>182269</t>
+          <t>180618</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>215992</t>
+          <t>214579</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,5%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42430</t>
+          <t>42185</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63289</t>
+          <t>63380</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42464</t>
+          <t>42440</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64132</t>
+          <t>63868</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>90721</t>
+          <t>91193</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>120657</t>
+          <t>120274</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,87%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>42757</t>
+          <t>42761</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63010</t>
+          <t>62746</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49359</t>
+          <t>49443</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71715</t>
+          <t>71309</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>97821</t>
+          <t>99517</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>126921</t>
+          <t>128448</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>64762</t>
+          <t>64890</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>84517</t>
+          <t>85630</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60104</t>
+          <t>58900</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>79291</t>
+          <t>79772</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>130737</t>
+          <t>132723</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>159156</t>
+          <t>158442</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,82%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15579</t>
+          <t>15744</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30043</t>
+          <t>29784</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18819</t>
+          <t>19001</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33958</t>
+          <t>34141</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>38084</t>
+          <t>37802</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>59346</t>
+          <t>58635</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36011</t>
+          <t>36976</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54499</t>
+          <t>54796</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32497</t>
+          <t>32136</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50812</t>
+          <t>50047</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74394</t>
+          <t>74403</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99672</t>
+          <t>99434</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16753</t>
+          <t>16529</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28587</t>
+          <t>28416</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26509</t>
+          <t>26826</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41077</t>
+          <t>41224</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>47406</t>
+          <t>47499</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>65034</t>
+          <t>65536</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>54,03%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14584</t>
+          <t>14322</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25526</t>
+          <t>25873</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15288</t>
+          <t>14835</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28145</t>
+          <t>27532</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32530</t>
+          <t>33208</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>49656</t>
+          <t>50460</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,6%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>13996</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10489</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22818</t>
+          <t>22265</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16551</t>
+          <t>16834</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32035</t>
+          <t>32721</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>291594</t>
+          <t>291716</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>334563</t>
+          <t>335179</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>314236</t>
+          <t>316636</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>357825</t>
+          <t>359337</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>623573</t>
+          <t>620997</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>681795</t>
+          <t>680837</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,93%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>143387</t>
+          <t>140895</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>179201</t>
+          <t>175850</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>169111</t>
+          <t>170129</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>209057</t>
+          <t>204665</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>324619</t>
+          <t>319942</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>375332</t>
+          <t>374864</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>159234</t>
+          <t>158996</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>197695</t>
+          <t>197435</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>144031</t>
+          <t>142879</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>180106</t>
+          <t>178883</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>313318</t>
+          <t>313923</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>366610</t>
+          <t>365816</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,37%</t>
         </is>
       </c>
     </row>
@@ -7584,12 +7584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19305</t>
+          <t>19732</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32699</t>
+          <t>33384</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27809</t>
+          <t>27949</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42726</t>
+          <t>43053</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50530</t>
+          <t>51257</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71104</t>
+          <t>72317</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,96%</t>
         </is>
       </c>
     </row>
@@ -7697,12 +7697,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21608</t>
+          <t>21314</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35684</t>
+          <t>35131</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19453</t>
+          <t>19125</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33697</t>
+          <t>33023</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45140</t>
+          <t>43633</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64084</t>
+          <t>64034</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20114</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32808</t>
+          <t>33814</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23993</t>
+          <t>24132</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39291</t>
+          <t>39090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>47957</t>
+          <t>48454</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68357</t>
+          <t>69086</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>40,09%</t>
         </is>
       </c>
     </row>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40701</t>
+          <t>40281</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56339</t>
+          <t>56675</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30181</t>
+          <t>29866</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45972</t>
+          <t>45244</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>74625</t>
+          <t>74714</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>97182</t>
+          <t>96850</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,84%</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20022</t>
+          <t>20296</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34531</t>
+          <t>34485</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30505</t>
+          <t>30507</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46850</t>
+          <t>47236</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>55144</t>
+          <t>54664</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>77089</t>
+          <t>76485</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19717</t>
+          <t>19713</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34602</t>
+          <t>34193</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22273</t>
+          <t>22843</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37487</t>
+          <t>37646</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44971</t>
+          <t>45849</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65291</t>
+          <t>67607</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17417</t>
+          <t>16808</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29412</t>
+          <t>28853</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27023</t>
+          <t>26598</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41031</t>
+          <t>40618</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>47739</t>
+          <t>48237</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>66176</t>
+          <t>67191</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8581,12 +8581,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,7%</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>15076</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26570</t>
+          <t>27137</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14725</t>
+          <t>14366</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27840</t>
+          <t>26792</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33037</t>
+          <t>32817</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50679</t>
+          <t>49685</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,49%</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8722,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9709</t>
+          <t>10368</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20916</t>
+          <t>21117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13731</t>
+          <t>13975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26374</t>
+          <t>26376</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26018</t>
+          <t>26242</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42481</t>
+          <t>43286</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,66%</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>79954</t>
+          <t>79691</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>102682</t>
+          <t>102724</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77803</t>
+          <t>79313</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>101809</t>
+          <t>101297</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>167649</t>
+          <t>164340</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>198981</t>
+          <t>198709</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,65%</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41589</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62010</t>
+          <t>62256</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37940</t>
+          <t>37640</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58842</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84353</t>
+          <t>84008</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>113861</t>
+          <t>112151</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59809</t>
+          <t>59570</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>81789</t>
+          <t>82243</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55649</t>
+          <t>54409</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>76943</t>
+          <t>77028</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>120397</t>
+          <t>120942</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>152284</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -9408,12 +9408,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>64887</t>
+          <t>63529</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>83691</t>
+          <t>82324</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47875</t>
+          <t>48654</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67203</t>
+          <t>67447</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>117071</t>
+          <t>117016</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>144477</t>
+          <t>145208</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9493,12 +9493,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,35%</t>
         </is>
       </c>
     </row>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18667</t>
+          <t>18140</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>33829</t>
+          <t>33194</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26052</t>
+          <t>25672</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42125</t>
+          <t>42013</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>48218</t>
+          <t>46902</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>71059</t>
+          <t>69991</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -9634,12 +9634,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24922</t>
+          <t>25287</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40233</t>
+          <t>40941</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36161</t>
+          <t>35308</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54917</t>
+          <t>54471</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65474</t>
+          <t>65636</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90349</t>
+          <t>90101</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,72%</t>
         </is>
       </c>
     </row>
@@ -9864,12 +9864,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20081</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32623</t>
+          <t>32723</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22230</t>
+          <t>21967</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>35329</t>
+          <t>35918</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>44815</t>
+          <t>45573</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>63796</t>
+          <t>63116</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,48%</t>
         </is>
       </c>
     </row>
@@ -9977,12 +9977,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7809</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17502</t>
+          <t>18237</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10912</t>
+          <t>10893</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22093</t>
+          <t>21808</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21184</t>
+          <t>20813</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35904</t>
+          <t>36078</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,28%</t>
         </is>
       </c>
     </row>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16467</t>
+          <t>16118</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28365</t>
+          <t>28448</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16904</t>
+          <t>16742</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29426</t>
+          <t>30103</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>36330</t>
+          <t>36472</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>54214</t>
+          <t>54754</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,92%</t>
         </is>
       </c>
     </row>
@@ -10320,12 +10320,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>269852</t>
+          <t>268474</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>310758</t>
+          <t>307232</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>261017</t>
+          <t>261063</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>303927</t>
+          <t>303379</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>542914</t>
+          <t>541416</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>599429</t>
+          <t>602539</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10405,12 +10405,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,53%</t>
         </is>
       </c>
     </row>
@@ -10433,12 +10433,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>146530</t>
+          <t>148052</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>183197</t>
+          <t>183517</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>161405</t>
+          <t>161870</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>200254</t>
+          <t>200532</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>321606</t>
+          <t>317341</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>371269</t>
+          <t>370688</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,01%</t>
         </is>
       </c>
     </row>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>174015</t>
+          <t>174371</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>210832</t>
+          <t>211731</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>193786</t>
+          <t>193834</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>235135</t>
+          <t>232747</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>381460</t>
+          <t>377161</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>438070</t>
+          <t>433523</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
